--- a/cp-date/ig/StructureDefinition-pdsm-simplified-publish.xlsx
+++ b/cp-date/ig/StructureDefinition-pdsm-simplified-publish.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-05T12:13:06+00:00</t>
+    <t>2026-05-05T12:29:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/cp-date/ig/StructureDefinition-pdsm-simplified-publish.xlsx
+++ b/cp-date/ig/StructureDefinition-pdsm-simplified-publish.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-05T12:29:58+00:00</t>
+    <t>2026-05-06T12:23:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -5101,7 +5101,7 @@
       </c>
       <c r="E26" s="2"/>
       <c r="F26" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="G26" t="s" s="2">
         <v>93</v>
